--- a/megamek/docs/MegaMek_Quirks_Reference.xlsx
+++ b/megamek/docs/MegaMek_Quirks_Reference.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -493,6 +493,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -518,7 +519,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Every MegaMek unit + weapon quirk: code, effect, MM Supported (YES/NO), rules ref</t>
+          <t>Every MegaMek unit + weapon quirk: code, effect, MM Supported (YES/PARTIAL/NO), rules ref</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -592,6 +593,21 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>This project</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Reconciled against the MegaMek engine on 2026-08-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>'MM Supported' is YES (rule takes effect), PARTIAL (some effect, not the printed rule) or NO (option exists but the engine ignores it). Statuses are mirrored in the quirks' .working keys in megamek/resources/megamek/common/options/messages.properties, which QuirkCatalog.java reads.</t>
         </is>
       </c>
     </row>
@@ -606,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -672,7 +688,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -992,7 +1008,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1056,7 +1072,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1312,7 +1328,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1344,7 +1360,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1856,7 +1872,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1888,7 +1904,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2656,7 +2672,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2880,7 +2896,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3744,7 +3760,7 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -4134,6 +4150,70 @@
       <c r="F110" s="4" t="inlineStr">
         <is>
           <t>CO p.208</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Directional Torso Mount (360)</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>directional_torso_mount_360</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>BMM p.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Directional Torso Mounted Weapon (360)</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>direct_torso_mount_quad</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>BMM p.83</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4862,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5278,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PARTIAL</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6266,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7539,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PARTIAL</t>
         </is>
       </c>
     </row>
@@ -7927,7 +8007,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
